--- a/docs/verification/files/rocscience/rs2_67e.xlsx
+++ b/docs/verification/files/rocscience/rs2_67e.xlsx
@@ -14274,9 +14274,6 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14541,7 +14538,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$6</formula1>
+      <formula1>$T$4:$T$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15839,7 +15836,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>32000.0</v>
       </c>
